--- a/travel_booking_forms/050_sustainable_travel_checklist--travel_booking_forms.xlsx
+++ b/travel_booking_forms/050_sustainable_travel_checklist--travel_booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Question</t>
+          <t>To encourage sustainable travel, we want to get to know a little about you.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Another Question</t>
+          <t>What is your primary mode of transportation for your next trip?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Another Question</t>
+          <t>How do you usually book your travel accommodations?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yet Another Question</t>
+          <t>Do you consider sustainable travel practices as important when making your travel decisions?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Have you participated in any eco-tourism activities?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Another Question</t>
+          <t>Which of the following actions do you take to reduce your environmental impact?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yet Another Question</t>
+          <t>How often do you offset flights?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Another Question</t>
+          <t>Do you prefer sustainable accommodations?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>How likely are you to choose accommodations with eco-friendly practices?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Another Question</t>
+          <t>Do you usually take public transport to get to your destinations?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>How often do you choose local tour operators for your activities?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,149 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yet Another Question</t>
+          <t>Do you use a refillable water bottle during your trip?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>user_input_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>user_input_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Another Question</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>user_input_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>user_input_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Yet Another Question</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>user_input_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>user_input_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Another Question</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -970,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1004,274 +866,274 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_input_4_choices</t>
+          <t>user_input_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_input_4_choices</t>
+          <t>user_input_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_input_4_choices</t>
+          <t>user_input_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>user_input_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>user_input_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>user_input_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>user_input_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>user_input_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>user_input_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_input_9_choices</t>
+          <t>user_input_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_input_9_choices</t>
+          <t>user_input_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_input_9_choices</t>
+          <t>user_input_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_input_11_choices</t>
+          <t>user_input_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_input_11_choices</t>
+          <t>user_input_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_input_11_choices</t>
+          <t>user_input_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>user_input_7_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1288,7 +1150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>user_input_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1305,7 +1167,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>user_input_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1322,7 +1184,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>user_input_8_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1339,7 +1201,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>user_input_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1356,7 +1218,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>user_input_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1373,7 +1235,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>user_input_9_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1390,7 +1252,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>user_input_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1407,7 +1269,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>user_input_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1416,6 +1278,108 @@
         </is>
       </c>
       <c r="C28" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>user_input_10_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>user_input_10_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>user_input_10_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>user_input_11_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>user_input_11_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>user_input_11_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
